--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="398">
   <si>
     <t>Property</t>
   </si>
@@ -595,7 +595,7 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -841,9 +841,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.version</t>
@@ -5210,7 +5207,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5281,7 +5278,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>219</v>
@@ -5395,7 +5392,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>226</v>
@@ -5438,10 +5435,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5509,7 +5506,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>232</v>
@@ -5623,7 +5620,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>238</v>
@@ -5739,7 +5736,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>247</v>
@@ -5855,14 +5852,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5884,10 +5881,10 @@
         <v>179</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5899,7 +5896,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -5918,7 +5915,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5936,7 +5933,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -5951,28 +5948,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5991,19 +5988,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6052,7 +6049,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6067,28 +6064,28 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6107,19 +6104,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6168,7 +6165,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6183,28 +6180,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6223,19 +6220,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6284,7 +6281,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6299,28 +6296,28 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6339,19 +6336,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6400,7 +6397,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6418,25 +6415,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6455,19 +6452,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6516,7 +6513,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6531,28 +6528,28 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6571,19 +6568,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6632,7 +6629,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6647,24 +6644,24 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6687,19 +6684,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6748,7 +6745,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6766,10 +6763,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6777,14 +6774,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6803,19 +6800,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6864,7 +6861,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6882,10 +6879,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6893,10 +6890,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6919,16 +6916,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6978,7 +6975,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6999,7 +6996,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7007,14 +7004,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7033,19 +7030,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7094,7 +7091,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7112,10 +7109,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7123,10 +7120,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7235,10 +7232,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7349,14 +7346,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7378,10 +7375,10 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>140</v>
@@ -7436,7 +7433,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7465,10 +7462,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7494,16 +7491,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7552,7 +7549,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7573,7 +7570,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7581,10 +7578,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7607,16 +7604,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7666,7 +7663,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>91</v>
@@ -7687,7 +7684,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7695,14 +7692,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7724,14 +7721,14 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7780,7 +7777,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7798,10 +7795,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7809,10 +7806,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7838,13 +7835,13 @@
         <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7873,11 +7870,11 @@
         <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
       </c>
@@ -7894,7 +7891,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7912,10 +7909,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7923,10 +7920,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7949,19 +7946,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8010,7 +8007,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8028,10 +8025,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -273,7 +273,7 @@
 【JP Core仕様】口腔診査結果レポートのプロファイル</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
 【JP Core仕様】DiagnosticReportリソースの共通プロファイル</t>
   </si>
   <si>
@@ -822,6 +822,15 @@
     <t>【JP Core仕様】レポートカテゴリーとして、LoincコードのLP31759-1（歯科口腔）を使用する。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP31759-1"/&gt;
+    &lt;display value="歯科口腔"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
@@ -847,9 +856,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.code</t>
-  </si>
-  <si>
-    <t>LP31759-1</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.display</t>
@@ -938,7 +944,7 @@
 </t>
   </si>
   <si>
-    <t>依頼時におけるヘルスケアイベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
+    <t>依頼時における診療イベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
   </si>
   <si>
     <t>例：診療、歯科健診（検診）、身元不明者調査 ※JP Coreに網羅されていない</t>
@@ -4528,7 +4534,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4547,7 +4553,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4594,7 +4600,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>190</v>
@@ -4706,7 +4712,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>196</v>
@@ -4820,7 +4826,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>201</v>
@@ -4936,7 +4942,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>210</v>
@@ -5048,7 +5054,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>211</v>
@@ -5162,7 +5168,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>212</v>
@@ -5278,7 +5284,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>219</v>
@@ -5392,7 +5398,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>226</v>
@@ -5438,7 +5444,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>268</v>
+        <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
